--- a/data/flux-summary-jwp.xlsx
+++ b/data/flux-summary-jwp.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Desktop/francois-remnant-prairie-main/flux-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gawainmacneacail/Documents/Research/Writing/2025 Junior Remnant Prairie/francois-remnant-prairie-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C6D542-4838-9A48-AA13-C0F31449E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79156C7C-5B0F-2B47-B494-615C06FFCEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28240" windowHeight="16440" firstSheet="2" activeTab="15" xr2:uid="{E798D32C-BD75-794C-B0D3-CC1EC84BEC45}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28240" windowHeight="16440" firstSheet="5" activeTab="15" xr2:uid="{E798D32C-BD75-794C-B0D3-CC1EC84BEC45}"/>
   </bookViews>
   <sheets>
-    <sheet name="8_12_22" sheetId="1" r:id="rId1"/>
-    <sheet name="9_2_22" sheetId="2" r:id="rId2"/>
-    <sheet name="9_16_22" sheetId="3" r:id="rId3"/>
-    <sheet name="9_30_22" sheetId="4" r:id="rId4"/>
-    <sheet name="9_7_22" sheetId="5" r:id="rId5"/>
-    <sheet name="22_7_22" sheetId="6" r:id="rId6"/>
-    <sheet name="22_10_19" sheetId="7" r:id="rId7"/>
-    <sheet name="22-11_02" sheetId="8" r:id="rId8"/>
-    <sheet name="3_22_2023" sheetId="9" r:id="rId9"/>
-    <sheet name="5_18_2023" sheetId="10" r:id="rId10"/>
-    <sheet name="6_2_2023" sheetId="11" r:id="rId11"/>
-    <sheet name="6_15_2023" sheetId="12" r:id="rId12"/>
-    <sheet name="7_6_2023" sheetId="13" r:id="rId13"/>
-    <sheet name="7_18_2023" sheetId="14" r:id="rId14"/>
-    <sheet name="8_2_2023" sheetId="15" r:id="rId15"/>
-    <sheet name="8_18_2023" sheetId="16" r:id="rId16"/>
+    <sheet name="220812-fluxes" sheetId="1" r:id="rId1"/>
+    <sheet name="220902-fluxes" sheetId="2" r:id="rId2"/>
+    <sheet name="220916-fluxes" sheetId="3" r:id="rId3"/>
+    <sheet name="220930-fluxes" sheetId="4" r:id="rId4"/>
+    <sheet name="220709-fluxes" sheetId="5" r:id="rId5"/>
+    <sheet name="220722-fluxes" sheetId="6" r:id="rId6"/>
+    <sheet name="221019-fluxes" sheetId="7" r:id="rId7"/>
+    <sheet name="221102-fluxes" sheetId="8" r:id="rId8"/>
+    <sheet name="230322-fluxes" sheetId="9" r:id="rId9"/>
+    <sheet name="230518-fluxes" sheetId="10" r:id="rId10"/>
+    <sheet name="230602-fluxes" sheetId="11" r:id="rId11"/>
+    <sheet name="230615-fluxes" sheetId="12" r:id="rId12"/>
+    <sheet name="230706-fluxes" sheetId="13" r:id="rId13"/>
+    <sheet name="230718-fluxes" sheetId="14" r:id="rId14"/>
+    <sheet name="230802-fluxes" sheetId="15" r:id="rId15"/>
+    <sheet name="230818-fluxes" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4302" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="56">
   <si>
     <t>date_collected</t>
   </si>
@@ -143,9 +143,6 @@
     <t>23/03/22</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inudated </t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>23/08/18</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -2093,8 +2093,18 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
@@ -2112,9 +2122,20 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>44785</v>
       </c>
@@ -2130,23 +2151,35 @@
       <c r="E49" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G54" s="2"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H57" s="2"/>
     </row>
   </sheetData>
@@ -2197,7 +2230,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -2221,12 +2254,12 @@
         <v>472.46</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -2250,12 +2283,12 @@
         <v>2.5367999999999999</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -2279,12 +2312,12 @@
         <v>0.45979999999999999</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -2308,12 +2341,12 @@
         <v>494.72</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -2337,12 +2370,12 @@
         <v>2.8631000000000002</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -2369,12 +2402,12 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -2398,12 +2431,12 @@
         <v>522.37</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -2427,12 +2460,12 @@
         <v>2.3696999999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -2456,15 +2489,15 @@
         <v>4.8500000000000001E-2</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -2488,12 +2521,12 @@
         <v>462.93</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -2517,12 +2550,12 @@
         <v>2.4922</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -2549,12 +2582,12 @@
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -2578,12 +2611,12 @@
         <v>487.64</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -2607,15 +2640,15 @@
         <v>2.2719</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -2639,12 +2672,12 @@
         <v>0.4556</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -2668,12 +2701,12 @@
         <v>555.86</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -2697,12 +2730,12 @@
         <v>2.3544999999999998</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -2726,15 +2759,15 @@
         <v>0.50229999999999997</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -2758,12 +2791,12 @@
         <v>491.06</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -2787,15 +2820,15 @@
         <v>2.3546</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -2822,12 +2855,12 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -2851,12 +2884,12 @@
         <v>566.21</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -2883,12 +2916,12 @@
         <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -2912,15 +2945,15 @@
         <v>5.79E-2</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -2944,12 +2977,12 @@
         <v>536.9</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -2973,12 +3006,12 @@
         <v>2.286</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -3005,12 +3038,12 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -3034,12 +3067,12 @@
         <v>529.89</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -3063,12 +3096,12 @@
         <v>2.3159000000000001</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -3095,12 +3128,12 @@
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -3124,12 +3157,12 @@
         <v>537.82000000000005</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -3153,15 +3186,15 @@
         <v>2.2921999999999998</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -3185,7 +3218,7 @@
         <v>5.7700000000000001E-2</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J34" t="s">
         <v>23</v>
@@ -3193,7 +3226,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -3217,12 +3250,12 @@
         <v>505.44</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -3246,7 +3279,7 @@
         <v>2.3357000000000001</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
         <v>23</v>
@@ -3254,7 +3287,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -3281,12 +3314,12 @@
         <v>13</v>
       </c>
       <c r="J37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -3310,12 +3343,12 @@
         <v>565.75</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -3339,12 +3372,12 @@
         <v>2.2812999999999999</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -3368,15 +3401,15 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -3400,12 +3433,12 @@
         <v>541.15</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -3429,15 +3462,15 @@
         <v>2.2566999999999999</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -3461,15 +3494,15 @@
         <v>5.74E-2</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -3493,12 +3526,12 @@
         <v>518.16</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -3522,12 +3555,12 @@
         <v>2.2955000000000001</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -3551,15 +3584,15 @@
         <v>0.48649999999999999</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -3583,12 +3616,12 @@
         <v>566.27</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -3615,12 +3648,12 @@
         <v>13</v>
       </c>
       <c r="J48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -3644,10 +3677,10 @@
         <v>0.49399999999999999</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3699,7 +3732,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -3723,15 +3756,15 @@
         <v>544.54</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -3758,12 +3791,12 @@
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -3790,12 +3823,12 @@
         <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -3819,15 +3852,15 @@
         <v>567.71</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -3851,15 +3884,15 @@
         <v>2.4557000000000002</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -3886,12 +3919,12 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -3915,15 +3948,15 @@
         <v>525.70000000000005</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -3947,15 +3980,15 @@
         <v>2.3589000000000002</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -3982,12 +4015,12 @@
         <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -4011,15 +4044,15 @@
         <v>500.69</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -4043,15 +4076,15 @@
         <v>2.3609</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -4075,15 +4108,15 @@
         <v>1.5072000000000001</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -4107,15 +4140,15 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -4142,12 +4175,12 @@
         <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -4174,12 +4207,12 @@
         <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -4203,15 +4236,15 @@
         <v>496.42</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -4238,12 +4271,12 @@
         <v>13</v>
       </c>
       <c r="J18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -4270,12 +4303,12 @@
         <v>13</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -4299,15 +4332,15 @@
         <v>489.3</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -4331,15 +4364,15 @@
         <v>2.3325</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -4366,12 +4399,12 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -4395,15 +4428,15 @@
         <v>545.41</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -4427,15 +4460,15 @@
         <v>2.4775</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -4462,12 +4495,12 @@
         <v>13</v>
       </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -4491,15 +4524,15 @@
         <v>582.07000000000005</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -4526,12 +4559,12 @@
         <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -4555,15 +4588,15 @@
         <v>1.5419</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -4587,15 +4620,15 @@
         <v>584.09</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -4619,15 +4652,15 @@
         <v>2.2869000000000002</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -4654,12 +4687,12 @@
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -4683,15 +4716,15 @@
         <v>592.54</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -4718,12 +4751,12 @@
         <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -4747,15 +4780,15 @@
         <v>1.5114000000000001</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -4779,15 +4812,15 @@
         <v>572.79999999999995</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -4814,12 +4847,12 @@
         <v>13</v>
       </c>
       <c r="J36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -4843,15 +4876,15 @@
         <v>1.5051000000000001</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -4878,12 +4911,12 @@
         <v>13</v>
       </c>
       <c r="J38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -4907,15 +4940,15 @@
         <v>2.3153000000000001</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -4942,12 +4975,12 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -4971,15 +5004,15 @@
         <v>564.79999999999995</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -5006,12 +5039,12 @@
         <v>13</v>
       </c>
       <c r="J42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -5038,12 +5071,12 @@
         <v>13</v>
       </c>
       <c r="J43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -5070,12 +5103,12 @@
         <v>13</v>
       </c>
       <c r="J44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -5102,12 +5135,12 @@
         <v>13</v>
       </c>
       <c r="J45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -5131,15 +5164,15 @@
         <v>1.3498000000000001</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -5163,15 +5196,15 @@
         <v>504.85</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -5198,12 +5231,12 @@
         <v>13</v>
       </c>
       <c r="J48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -5230,7 +5263,7 @@
         <v>13</v>
       </c>
       <c r="J49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5280,7 +5313,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -5304,12 +5337,12 @@
         <v>588.54</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -5333,15 +5366,15 @@
         <v>2.3056000000000001</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -5365,15 +5398,15 @@
         <v>0.3715</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -5397,12 +5430,12 @@
         <v>515.76</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -5429,12 +5462,12 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -5458,15 +5491,15 @@
         <v>0.38969999999999999</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -5490,12 +5523,12 @@
         <v>524.86</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -5519,15 +5552,15 @@
         <v>2.2456</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -5554,12 +5587,12 @@
         <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -5583,12 +5616,12 @@
         <v>494</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -5612,15 +5645,15 @@
         <v>2.2724000000000002</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -5647,12 +5680,12 @@
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -5676,12 +5709,12 @@
         <v>544.75</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -5705,12 +5738,12 @@
         <v>2.2805</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -5734,15 +5767,15 @@
         <v>0.36609999999999998</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -5766,12 +5799,12 @@
         <v>552.53</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -5795,12 +5828,12 @@
         <v>2.258</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -5824,7 +5857,7 @@
         <v>0.40200000000000002</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
         <v>23</v>
@@ -5832,7 +5865,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -5856,12 +5889,12 @@
         <v>513.15</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -5885,12 +5918,12 @@
         <v>2.3504</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -5914,7 +5947,7 @@
         <v>0.39879999999999999</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
         <v>23</v>
@@ -5922,7 +5955,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -5946,12 +5979,12 @@
         <v>519.62</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -5975,12 +6008,12 @@
         <v>2.2942</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -6007,12 +6040,12 @@
         <v>13</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -6036,12 +6069,12 @@
         <v>531.27</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -6065,12 +6098,12 @@
         <v>2.327</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -6094,7 +6127,7 @@
         <v>0.40539999999999998</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
         <v>23</v>
@@ -6102,7 +6135,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -6126,12 +6159,12 @@
         <v>538.13</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -6155,12 +6188,12 @@
         <v>2.3475000000000001</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -6187,12 +6220,12 @@
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -6216,12 +6249,12 @@
         <v>530.71</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -6245,12 +6278,12 @@
         <v>2.3384</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -6277,12 +6310,12 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -6306,12 +6339,12 @@
         <v>518.58000000000004</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -6335,12 +6368,12 @@
         <v>2.2907999999999999</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -6364,15 +6397,15 @@
         <v>0.40510000000000002</v>
       </c>
       <c r="I37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -6396,12 +6429,12 @@
         <v>588.59</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -6425,12 +6458,12 @@
         <v>2.234</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -6457,12 +6490,12 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -6486,12 +6519,12 @@
         <v>622.45000000000005</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -6517,7 +6550,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -6541,15 +6574,15 @@
         <v>0.39579999999999999</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -6573,12 +6606,12 @@
         <v>544.08000000000004</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -6602,15 +6635,15 @@
         <v>2.2151000000000001</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -6637,12 +6670,12 @@
         <v>13</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -6666,12 +6699,12 @@
         <v>546.48</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -6695,15 +6728,15 @@
         <v>2.2355999999999998</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -6730,7 +6763,7 @@
         <v>13</v>
       </c>
       <c r="J49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6780,7 +6813,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -6804,12 +6837,12 @@
         <v>522.79999999999995</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -6836,12 +6869,12 @@
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -6865,15 +6898,15 @@
         <v>0.63360000000000005</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -6897,12 +6930,12 @@
         <v>639.13</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -6926,15 +6959,15 @@
         <v>2.2924000000000002</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -6961,12 +6994,12 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -6990,12 +7023,12 @@
         <v>563.4</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -7019,15 +7052,15 @@
         <v>3.7233000000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -7054,12 +7087,12 @@
         <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -7083,12 +7116,12 @@
         <v>492.29</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -7115,12 +7148,12 @@
         <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -7144,15 +7177,15 @@
         <v>9.3299999999999994E-2</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -7176,12 +7209,12 @@
         <v>520.07000000000005</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -7208,12 +7241,12 @@
         <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -7240,12 +7273,12 @@
         <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -7269,12 +7302,12 @@
         <v>519.77</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -7298,15 +7331,15 @@
         <v>2.8288000000000002</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -7330,12 +7363,12 @@
         <v>0.81430000000000002</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -7359,12 +7392,12 @@
         <v>611.42999999999995</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -7391,12 +7424,12 @@
         <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -7423,12 +7456,12 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -7452,12 +7485,12 @@
         <v>586.80999999999995</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -7481,15 +7514,15 @@
         <v>2.2454999999999998</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -7513,15 +7546,15 @@
         <v>0.1704</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -7545,12 +7578,12 @@
         <v>567.77</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -7577,12 +7610,12 @@
         <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -7609,12 +7642,12 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -7638,12 +7671,12 @@
         <v>546.04</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -7667,15 +7700,15 @@
         <v>2.7238000000000002</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -7699,15 +7732,15 @@
         <v>0.81759999999999999</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -7731,12 +7764,12 @@
         <v>511.96</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -7763,12 +7796,12 @@
         <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -7795,12 +7828,12 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -7824,12 +7857,12 @@
         <v>834.36</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -7856,12 +7889,12 @@
         <v>13</v>
       </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -7885,15 +7918,15 @@
         <v>9.8599999999999993E-2</v>
       </c>
       <c r="I37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -7917,12 +7950,12 @@
         <v>543.57000000000005</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -7946,15 +7979,15 @@
         <v>2.5358000000000001</v>
       </c>
       <c r="I39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -7981,12 +8014,12 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -8010,15 +8043,15 @@
         <v>468.17</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -8045,12 +8078,12 @@
         <v>13</v>
       </c>
       <c r="J42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -8077,12 +8110,12 @@
         <v>13</v>
       </c>
       <c r="J43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -8106,15 +8139,15 @@
         <v>536.62</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -8138,15 +8171,15 @@
         <v>2.3414000000000001</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -8170,15 +8203,15 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -8202,15 +8235,15 @@
         <v>483.44</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -8237,12 +8270,12 @@
         <v>13</v>
       </c>
       <c r="J48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -8269,7 +8302,7 @@
         <v>13</v>
       </c>
       <c r="J49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -8319,7 +8352,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -8343,12 +8376,12 @@
         <v>476.59</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -8372,15 +8405,15 @@
         <v>2.2698</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -8404,15 +8437,15 @@
         <v>0.38</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -8436,12 +8469,12 @@
         <v>476.5</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -8465,15 +8498,15 @@
         <v>2.2494999999999998</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -8497,7 +8530,7 @@
         <v>0.40960000000000002</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
         <v>23</v>
@@ -8505,7 +8538,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -8529,12 +8562,12 @@
         <v>511.59</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -8561,12 +8594,12 @@
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -8590,7 +8623,7 @@
         <v>0.41270000000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
         <v>23</v>
@@ -8598,7 +8631,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -8622,12 +8655,12 @@
         <v>541.97</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -8654,12 +8687,12 @@
         <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -8683,15 +8716,15 @@
         <v>0.38219999999999998</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -8715,15 +8748,15 @@
         <v>489.78</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -8747,15 +8780,15 @@
         <v>2.2543000000000002</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -8779,15 +8812,15 @@
         <v>0.38419999999999999</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -8811,15 +8844,15 @@
         <v>494.58</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -8843,15 +8876,15 @@
         <v>2.2827999999999999</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -8878,12 +8911,12 @@
         <v>13</v>
       </c>
       <c r="J19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -8907,15 +8940,15 @@
         <v>527.21</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -8939,15 +8972,15 @@
         <v>2.3475999999999999</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -8974,12 +9007,12 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -9003,15 +9036,15 @@
         <v>460.24</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -9035,15 +9068,15 @@
         <v>2.2927</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -9070,12 +9103,12 @@
         <v>13</v>
       </c>
       <c r="J25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -9099,12 +9132,12 @@
         <v>601.87</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -9128,12 +9161,12 @@
         <v>2.2824</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -9160,12 +9193,12 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -9189,12 +9222,12 @@
         <v>520.74</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -9218,12 +9251,12 @@
         <v>2.3147000000000002</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -9247,15 +9280,15 @@
         <v>0.3821</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -9279,12 +9312,12 @@
         <v>515.23</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -9308,12 +9341,12 @@
         <v>2.2881999999999998</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -9340,12 +9373,12 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -9369,12 +9402,12 @@
         <v>494.07</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -9398,12 +9431,12 @@
         <v>2.2852999999999999</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -9427,12 +9460,12 @@
         <v>0.38469999999999999</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -9456,15 +9489,15 @@
         <v>703.38</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -9488,15 +9521,15 @@
         <v>2.2829999999999999</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -9523,12 +9556,12 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -9552,15 +9585,15 @@
         <v>555.04</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -9584,15 +9617,15 @@
         <v>2.319</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -9619,12 +9652,12 @@
         <v>13</v>
       </c>
       <c r="J43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -9648,15 +9681,15 @@
         <v>447.37</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -9680,15 +9713,15 @@
         <v>2.3109000000000002</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -9715,12 +9748,12 @@
         <v>13</v>
       </c>
       <c r="J46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -9744,15 +9777,15 @@
         <v>494.9</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -9776,15 +9809,15 @@
         <v>2.3241000000000001</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -9808,10 +9841,10 @@
         <v>0.38469999999999999</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -9858,7 +9891,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -9882,12 +9915,12 @@
         <v>451.35</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -9911,15 +9944,15 @@
         <v>2.3205</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -9943,15 +9976,15 @@
         <v>0.31730000000000003</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -9975,12 +10008,12 @@
         <v>473.25</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -10004,7 +10037,7 @@
         <v>2.2728999999999999</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
         <v>23</v>
@@ -10012,7 +10045,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -10036,12 +10069,12 @@
         <v>0.2964</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -10065,12 +10098,12 @@
         <v>502.84</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -10094,7 +10127,7 @@
         <v>2.3018999999999998</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
         <v>23</v>
@@ -10102,7 +10135,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -10126,15 +10159,15 @@
         <v>0.3145</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -10158,12 +10191,12 @@
         <v>494.43</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -10187,15 +10220,15 @@
         <v>2.3159000000000001</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -10219,7 +10252,7 @@
         <v>0.29959999999999998</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
         <v>23</v>
@@ -10227,7 +10260,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -10251,12 +10284,12 @@
         <v>475.67</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -10280,15 +10313,15 @@
         <v>2.3772000000000002</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -10312,15 +10345,15 @@
         <v>0.31659999999999999</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -10344,12 +10377,12 @@
         <v>430.88</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -10376,12 +10409,12 @@
         <v>13</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -10405,7 +10438,7 @@
         <v>0.30180000000000001</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
         <v>23</v>
@@ -10413,7 +10446,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -10437,12 +10470,12 @@
         <v>495.53</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -10466,12 +10499,12 @@
         <v>2.2856000000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -10495,12 +10528,12 @@
         <v>0.31319999999999998</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -10524,12 +10557,12 @@
         <v>474.1</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -10553,12 +10586,12 @@
         <v>2.3048999999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -10582,7 +10615,7 @@
         <v>0.32650000000000001</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
         <v>23</v>
@@ -10590,7 +10623,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -10614,12 +10647,12 @@
         <v>495.34</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -10643,15 +10676,15 @@
         <v>2.2848000000000002</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -10678,12 +10711,12 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -10707,12 +10740,12 @@
         <v>491.75</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -10736,15 +10769,15 @@
         <v>2.2671999999999999</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -10768,7 +10801,7 @@
         <v>0.29189999999999999</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
         <v>23</v>
@@ -10776,7 +10809,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -10800,12 +10833,12 @@
         <v>500.35</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -10829,15 +10862,15 @@
         <v>2.2538999999999998</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -10864,12 +10897,12 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -10893,12 +10926,12 @@
         <v>455.59</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -10922,7 +10955,7 @@
         <v>2.2810999999999999</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
         <v>23</v>
@@ -10930,7 +10963,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -10957,12 +10990,12 @@
         <v>13</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -10986,12 +11019,12 @@
         <v>472.15</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -11015,7 +11048,7 @@
         <v>2.3117000000000001</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
         <v>23</v>
@@ -11023,7 +11056,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -11050,12 +11083,12 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -11079,12 +11112,12 @@
         <v>474.83</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -11108,7 +11141,7 @@
         <v>2.3485999999999998</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
         <v>23</v>
@@ -11116,7 +11149,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -11140,15 +11173,15 @@
         <v>0.30259999999999998</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -11172,12 +11205,12 @@
         <v>474.87</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -11201,15 +11234,15 @@
         <v>2.3271000000000002</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -11233,15 +11266,15 @@
         <v>0.29730000000000001</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -11265,12 +11298,12 @@
         <v>505.52</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -11294,15 +11327,15 @@
         <v>2.2742</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -11326,10 +11359,10 @@
         <v>0.307</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -11380,7 +11413,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -11404,12 +11437,12 @@
         <v>410.92</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -11433,12 +11466,12 @@
         <v>2.2422</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -11462,15 +11495,15 @@
         <v>0.31090000000000001</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -11494,12 +11527,12 @@
         <v>414.69</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -11526,12 +11559,12 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -11558,12 +11591,12 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -11578,21 +11611,21 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -11607,21 +11640,21 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -11636,21 +11669,21 @@
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -11665,21 +11698,21 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -11694,21 +11727,21 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -11723,21 +11756,21 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -11752,21 +11785,21 @@
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -11781,21 +11814,21 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
@@ -11810,21 +11843,21 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
@@ -11839,21 +11872,21 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -11868,21 +11901,21 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -11897,21 +11930,21 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -11926,21 +11959,21 @@
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -11955,21 +11988,21 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -11984,21 +12017,21 @@
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -12013,21 +12046,21 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -12042,21 +12075,21 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -12071,21 +12104,21 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -12109,12 +12142,12 @@
         <v>456.82</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -12138,7 +12171,7 @@
         <v>2.2235</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
         <v>23</v>
@@ -12146,7 +12179,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -12170,7 +12203,7 @@
         <v>0.31069999999999998</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
         <v>23</v>
@@ -12178,7 +12211,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -12202,12 +12235,12 @@
         <v>465.95</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -12231,15 +12264,15 @@
         <v>2.2822</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -12263,15 +12296,15 @@
         <v>0.30709999999999998</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -12295,12 +12328,12 @@
         <v>436.15</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -12324,12 +12357,12 @@
         <v>2.2191999999999998</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -12353,12 +12386,12 @@
         <v>0.31309999999999999</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -12382,12 +12415,12 @@
         <v>545.04999999999995</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -12411,12 +12444,12 @@
         <v>2.3083</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -12440,15 +12473,15 @@
         <v>0.31269999999999998</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
@@ -12472,12 +12505,12 @@
         <v>467.81</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -12504,12 +12537,12 @@
         <v>13</v>
       </c>
       <c r="J39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -12533,12 +12566,12 @@
         <v>0.31130000000000002</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -12562,12 +12595,12 @@
         <v>451.4</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -12591,15 +12624,15 @@
         <v>2.2968000000000002</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -12623,12 +12656,12 @@
         <v>0.311</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -12652,12 +12685,12 @@
         <v>418.01</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
@@ -12684,12 +12717,12 @@
         <v>13</v>
       </c>
       <c r="J45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -12713,12 +12746,12 @@
         <v>0.313</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -12742,12 +12775,12 @@
         <v>431.04</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -12771,15 +12804,15 @@
         <v>2.2412000000000001</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -12803,7 +12836,7 @@
         <v>0.31390000000000001</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -14268,9 +14301,18 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
@@ -14288,11 +14330,20 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>44806</v>
       </c>
@@ -14308,43 +14359,52 @@
       <c r="E49" t="s">
         <v>15</v>
       </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H59" s="2"/>
     </row>
   </sheetData>
@@ -15813,9 +15873,18 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
@@ -15833,9 +15902,18 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="5"/>
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
@@ -15853,16 +15931,20 @@
       <c r="E49" t="s">
         <v>15</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F51" s="2"/>
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F52" s="2"/>
-      <c r="H52" s="2"/>
       <c r="J52" s="2"/>
       <c r="L52" s="2"/>
     </row>
@@ -17104,9 +17186,18 @@
       <c r="E38" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
+      <c r="F38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I38" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
@@ -17124,9 +17215,18 @@
       <c r="E39" t="s">
         <v>11</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="F39" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39" t="s">
+        <v>55</v>
+      </c>
+      <c r="I39" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
@@ -17144,9 +17244,18 @@
       <c r="E40" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" t="s">
+        <v>55</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
@@ -17165,9 +17274,18 @@
       <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
+      <c r="F41" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I41" t="s">
+        <v>55</v>
+      </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
@@ -17187,9 +17305,18 @@
       <c r="E42" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="F42" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" t="s">
+        <v>55</v>
+      </c>
       <c r="N42" s="2"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
@@ -17208,9 +17335,18 @@
       <c r="E43" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="5"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" t="s">
+        <v>55</v>
+      </c>
+      <c r="H43" t="s">
+        <v>55</v>
+      </c>
+      <c r="I43" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="F44" s="5"/>
@@ -17587,14 +17723,17 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>55</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -17615,14 +17754,17 @@
       <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -17643,14 +17785,17 @@
       <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
       </c>
       <c r="M13" s="2"/>
     </row>
@@ -17670,14 +17815,17 @@
       <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
       </c>
       <c r="M14" s="2"/>
     </row>
@@ -17697,14 +17845,17 @@
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" t="s">
+        <v>55</v>
       </c>
       <c r="N15" s="2"/>
     </row>
@@ -17724,14 +17875,17 @@
       <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" t="s">
+        <v>55</v>
       </c>
       <c r="L16" s="2"/>
       <c r="N16" s="2"/>
@@ -19169,14 +19323,17 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -19195,14 +19352,17 @@
       <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -19221,14 +19381,17 @@
       <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -19247,14 +19410,17 @@
       <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -19273,14 +19439,17 @@
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -19299,14 +19468,17 @@
       <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -23462,10 +23634,18 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="6"/>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
       <c r="J47" s="2"/>
       <c r="M47" s="2"/>
     </row>
@@ -23485,10 +23665,18 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="6"/>
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
     </row>
@@ -23508,10 +23696,18 @@
       <c r="E49" t="s">
         <v>15</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="6"/>
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" t="s">
+        <v>55</v>
+      </c>
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -23585,19 +23781,19 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" t="s">
         <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -23617,19 +23813,19 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -23649,19 +23845,19 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
         <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -23681,19 +23877,19 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
         <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -23713,19 +23909,19 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
         <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -23745,19 +23941,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -23777,19 +23973,19 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
         <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -23809,19 +24005,19 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
         <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -23841,19 +24037,19 @@
         <v>15</v>
       </c>
       <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" t="s">
         <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -23873,19 +24069,19 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" t="s">
         <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -23905,19 +24101,19 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" t="s">
         <v>30</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -23937,19 +24133,19 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" t="s">
         <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -23981,7 +24177,7 @@
         <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -24013,7 +24209,7 @@
         <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -24042,10 +24238,10 @@
         <v>0.35020000000000001</v>
       </c>
       <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
         <v>33</v>
-      </c>
-      <c r="J16" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -24065,19 +24261,19 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" t="s">
         <v>30</v>
-      </c>
-      <c r="G17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -24097,19 +24293,19 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" t="s">
         <v>30</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -24129,19 +24325,19 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" t="s">
         <v>30</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -24170,10 +24366,10 @@
         <v>483.24</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -24202,10 +24398,10 @@
         <v>2.2440000000000002</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -24237,7 +24433,7 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -24266,10 +24462,10 @@
         <v>482.98</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -24301,7 +24497,7 @@
         <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -24330,10 +24526,10 @@
         <v>0.34029999999999999</v>
       </c>
       <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
         <v>33</v>
-      </c>
-      <c r="J25" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -24362,7 +24558,7 @@
         <v>477.37</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -24391,7 +24587,7 @@
         <v>2.2511000000000001</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -24420,7 +24616,7 @@
         <v>0.3367</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -24449,10 +24645,10 @@
         <v>467.94</v>
       </c>
       <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
         <v>33</v>
-      </c>
-      <c r="J29" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -24481,10 +24677,10 @@
         <v>2.2566999999999999</v>
       </c>
       <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
         <v>33</v>
-      </c>
-      <c r="J30" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -24516,7 +24712,7 @@
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -24545,10 +24741,10 @@
         <v>469.86</v>
       </c>
       <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" t="s">
         <v>33</v>
-      </c>
-      <c r="J32" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -24580,7 +24776,7 @@
         <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -24612,7 +24808,7 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -24641,10 +24837,10 @@
         <v>476.21</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -24673,10 +24869,10 @@
         <v>2.2530999999999999</v>
       </c>
       <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
         <v>33</v>
-      </c>
-      <c r="J36" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -24705,10 +24901,10 @@
         <v>0.33739999999999998</v>
       </c>
       <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
         <v>33</v>
-      </c>
-      <c r="J37" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -24737,10 +24933,10 @@
         <v>479.69</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -24772,7 +24968,7 @@
         <v>13</v>
       </c>
       <c r="J39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -24804,7 +25000,7 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -24833,10 +25029,10 @@
         <v>491.4</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -24868,7 +25064,7 @@
         <v>13</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -24897,10 +25093,10 @@
         <v>0.33489999999999998</v>
       </c>
       <c r="I43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" t="s">
         <v>33</v>
-      </c>
-      <c r="J43" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -24929,10 +25125,10 @@
         <v>476.92</v>
       </c>
       <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
         <v>33</v>
-      </c>
-      <c r="J44" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -24961,10 +25157,10 @@
         <v>2.2303999999999999</v>
       </c>
       <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
         <v>33</v>
-      </c>
-      <c r="J45" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -24993,10 +25189,10 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -25028,7 +25224,7 @@
         <v>13</v>
       </c>
       <c r="J47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -25057,10 +25253,10 @@
         <v>2.2764000000000002</v>
       </c>
       <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
         <v>33</v>
-      </c>
-      <c r="J48" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -25089,10 +25285,10 @@
         <v>0.33750000000000002</v>
       </c>
       <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
         <v>33</v>
-      </c>
-      <c r="J49" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
